--- a/product_selector_out/STM32F0x8.xlsx
+++ b/product_selector_out/STM32F0x8.xlsx
@@ -42,7 +42,7 @@
       <sz val="11"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
@@ -74,6 +74,11 @@
         <fgColor rgb="00FFEB9C"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D9EAD3"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -90,7 +95,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="bottom"/>
@@ -105,6 +110,7 @@
     <xf numFmtId="0" fontId="2" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -7557,109 +7563,109 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="R13" s="9" t="inlineStr">
+      <c r="R13" s="10" t="inlineStr">
+        <is>
+          <t>DERIVED</t>
+        </is>
+      </c>
+      <c r="S13" s="10" t="inlineStr">
+        <is>
+          <t>DERIVED</t>
+        </is>
+      </c>
+      <c r="T13" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="U13" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="V13" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="W13" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="X13" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Y13" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Z13" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AA13" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AB13" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AC13" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AD13" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="AE13" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AF13" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AG13" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AH13" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="AI13" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AJ13" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="AK13" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="AL13" s="9" t="inlineStr">
         <is>
           <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="S13" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="T13" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="U13" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="V13" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="W13" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="X13" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Y13" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Z13" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AA13" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AB13" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AC13" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AD13" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
-        </is>
-      </c>
-      <c r="AE13" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AF13" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AG13" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AH13" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
-        </is>
-      </c>
-      <c r="AI13" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AJ13" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
-        </is>
-      </c>
-      <c r="AK13" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AL13" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AM13" s="8" t="inlineStr">
@@ -7884,109 +7890,109 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="R14" s="9" t="inlineStr">
+      <c r="R14" s="10" t="inlineStr">
+        <is>
+          <t>DERIVED</t>
+        </is>
+      </c>
+      <c r="S14" s="10" t="inlineStr">
+        <is>
+          <t>DERIVED</t>
+        </is>
+      </c>
+      <c r="T14" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="U14" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="V14" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="W14" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="X14" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Y14" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Z14" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AA14" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AB14" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AC14" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AD14" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="AE14" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AF14" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AG14" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AH14" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="AI14" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AJ14" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="AK14" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="AL14" s="9" t="inlineStr">
         <is>
           <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="S14" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="T14" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="U14" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="V14" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="W14" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="X14" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Y14" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Z14" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AA14" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AB14" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AC14" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AD14" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
-        </is>
-      </c>
-      <c r="AE14" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AF14" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AG14" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AH14" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
-        </is>
-      </c>
-      <c r="AI14" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AJ14" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
-        </is>
-      </c>
-      <c r="AK14" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AL14" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AM14" s="8" t="inlineStr">
@@ -8211,109 +8217,109 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="R15" s="9" t="inlineStr">
+      <c r="R15" s="10" t="inlineStr">
+        <is>
+          <t>DERIVED</t>
+        </is>
+      </c>
+      <c r="S15" s="10" t="inlineStr">
+        <is>
+          <t>DERIVED</t>
+        </is>
+      </c>
+      <c r="T15" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="U15" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="V15" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="W15" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="X15" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Y15" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Z15" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AA15" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AB15" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AC15" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AD15" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="AE15" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AF15" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AG15" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AH15" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="AI15" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AJ15" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="AK15" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="AL15" s="9" t="inlineStr">
         <is>
           <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="S15" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="T15" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="U15" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="V15" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="W15" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="X15" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Y15" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Z15" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AA15" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AB15" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AC15" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AD15" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
-        </is>
-      </c>
-      <c r="AE15" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AF15" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AG15" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AH15" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
-        </is>
-      </c>
-      <c r="AI15" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AJ15" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
-        </is>
-      </c>
-      <c r="AK15" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AL15" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AM15" s="8" t="inlineStr">
@@ -9519,109 +9525,109 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="R19" s="9" t="inlineStr">
+      <c r="R19" s="10" t="inlineStr">
+        <is>
+          <t>DERIVED</t>
+        </is>
+      </c>
+      <c r="S19" s="10" t="inlineStr">
+        <is>
+          <t>DERIVED</t>
+        </is>
+      </c>
+      <c r="T19" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="U19" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="V19" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="W19" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="X19" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Y19" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Z19" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AA19" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AB19" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AC19" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AD19" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="AE19" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AF19" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AG19" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AH19" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="AI19" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AJ19" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="AK19" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="AL19" s="9" t="inlineStr">
         <is>
           <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="S19" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="T19" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="U19" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="V19" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="W19" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="X19" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Y19" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Z19" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AA19" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AB19" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AC19" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AD19" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
-        </is>
-      </c>
-      <c r="AE19" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AF19" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AG19" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AH19" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
-        </is>
-      </c>
-      <c r="AI19" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AJ19" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
-        </is>
-      </c>
-      <c r="AK19" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AL19" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AM19" s="8" t="inlineStr">
@@ -10827,109 +10833,109 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="R23" s="9" t="inlineStr">
+      <c r="R23" s="10" t="inlineStr">
+        <is>
+          <t>DERIVED</t>
+        </is>
+      </c>
+      <c r="S23" s="10" t="inlineStr">
+        <is>
+          <t>DERIVED</t>
+        </is>
+      </c>
+      <c r="T23" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="U23" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="V23" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="W23" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="X23" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Y23" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Z23" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AA23" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AB23" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AC23" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AD23" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="AE23" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AF23" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AG23" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AH23" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="AI23" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AJ23" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="AK23" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="AL23" s="9" t="inlineStr">
         <is>
           <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="S23" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="T23" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="U23" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="V23" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="W23" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="X23" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Y23" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Z23" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AA23" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AB23" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AC23" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AD23" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
-        </is>
-      </c>
-      <c r="AE23" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AF23" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AG23" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AH23" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
-        </is>
-      </c>
-      <c r="AI23" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AJ23" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
-        </is>
-      </c>
-      <c r="AK23" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AL23" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AM23" s="8" t="inlineStr">
@@ -12718,7 +12724,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D40"/>
+  <dimension ref="A1:D35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -12823,7 +12829,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>USART typ</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -12833,19 +12839,19 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Table 5. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>summary row reads USART = 1 with no UART split; ST publishes USART and UART separately, so the cell's combined count answers neither column</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>STM32F038C6</t>
+          <t>STM32F038K6</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Package</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -12855,7 +12861,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Table 5. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 2. STM32F038x6 family device features and peripheral counts lists UFQFPN32 for this family; the table gives no key to tie a package to this part</t>
         </is>
       </c>
     </row>
@@ -12867,7 +12873,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Package</t>
+          <t>USART typ</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -12877,19 +12883,19 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Table 2. STM32F038x6 family device features and peripheral counts lists UFQFPN32 for this family; the table gives no key to tie a package to this part</t>
+          <t>summary row reads USART = 1 with no UART split; ST publishes USART and UART separately, so the cell's combined count answers neither column</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>STM32F038K6</t>
+          <t>STM32F038G6</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Package</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -12899,19 +12905,19 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Table 5. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 2. STM32F038x6 family device features and peripheral counts lists UFQFPN28 for this family; the table gives no key to tie a package to this part</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>STM32F038K6</t>
+          <t>STM32F038G6</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>USART typ</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -12921,19 +12927,19 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Table 5. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>summary row reads USART = 1 with no UART split; ST publishes USART and UART separately, so the cell's combined count answers neither column</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>STM32F038G6</t>
+          <t>STM32F098VC</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Package</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -12943,19 +12949,19 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Table 2. STM32F038x6 family device features and peripheral counts lists UFQFPN28 for this family; the table gives no key to tie a package to this part</t>
+          <t>Table 6. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>STM32F038G6</t>
+          <t>STM32F098VC</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Timers (32-bit) typ</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -12965,19 +12971,19 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Table 5. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 6. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>STM32F038G6</t>
+          <t>STM32F048T6</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -12987,19 +12993,19 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Table 5. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 6. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>STM32F098VC</t>
+          <t>STM32F048T6</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Timers (32-bit) typ</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -13016,12 +13022,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>STM32F098VC</t>
+          <t>STM32F098RC</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -13038,12 +13044,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>STM32F048T6</t>
+          <t>STM32F098RC</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Timers (32-bit) typ</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -13060,12 +13066,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>STM32F048T6</t>
+          <t>STM32F038F6</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Package</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -13075,19 +13081,19 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Table 6. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 2. STM32F038x6 family device features and peripheral counts lists TSSOP20 for this family; the table gives no key to tie a package to this part</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>STM32F098RC</t>
+          <t>STM32F038F6</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>USART typ</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -13097,19 +13103,19 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Table 6. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>summary row reads USART = 1 with no UART split; ST publishes USART and UART separately, so the cell's combined count answers neither column</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>STM32F098RC</t>
+          <t>STM32F058C8</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -13126,12 +13132,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>STM32F038F6</t>
+          <t>STM32F058C8</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Package</t>
+          <t>Timers (32-bit) typ</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -13141,14 +13147,14 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Table 2. STM32F038x6 family device features and peripheral counts lists TSSOP20 for this family; the table gives no key to tie a package to this part</t>
+          <t>Table 6. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>STM32F038F6</t>
+          <t>STM32F098CC</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -13163,14 +13169,14 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Table 5. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 6. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>STM32F038F6</t>
+          <t>STM32F098CC</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -13185,14 +13191,14 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Table 5. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 6. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>STM32F058C8</t>
+          <t>STM32F078CB</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -13214,7 +13220,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>STM32F058C8</t>
+          <t>STM32F078CB</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -13236,12 +13242,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>STM32F098CC</t>
+          <t>STM32F038E6</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Package</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -13251,19 +13257,19 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Table 6. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 2. STM32F038x6 family device features and peripheral counts lists WLCSP25 for this family; the table gives no key to tie a package to this part</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>STM32F098CC</t>
+          <t>STM32F038E6</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>USART typ</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -13273,14 +13279,14 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Table 6. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>summary row reads USART = 1 with no UART split; ST publishes USART and UART separately, so the cell's combined count answers neither column</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>STM32F078CB</t>
+          <t>STM32F078RB</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -13302,7 +13308,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>STM32F078CB</t>
+          <t>STM32F078RB</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -13324,12 +13330,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>STM32F038E6</t>
+          <t>STM32F058R8</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Package</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -13339,19 +13345,19 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Table 2. STM32F038x6 family device features and peripheral counts lists WLCSP25 for this family; the table gives no key to tie a package to this part</t>
+          <t>Table 6. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>STM32F038E6</t>
+          <t>STM32F058R8</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Timers (32-bit) typ</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -13361,19 +13367,19 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Table 5. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 6. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>STM32F038E6</t>
+          <t>STM32F048G6</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -13383,19 +13389,19 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Table 5. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 6. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>STM32F078RB</t>
+          <t>STM32F048G6</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Timers (32-bit) typ</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -13412,12 +13418,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>STM32F078RB</t>
+          <t>STM32F078VB</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -13434,12 +13440,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>STM32F058R8</t>
+          <t>STM32F078VB</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Timers (32-bit) typ</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -13456,12 +13462,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>STM32F058R8</t>
+          <t>STM32F048C6</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -13478,12 +13484,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>STM32F048G6</t>
+          <t>STM32F048C6</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Timers (32-bit) typ</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -13492,116 +13498,6 @@
         </is>
       </c>
       <c r="D35" t="inlineStr">
-        <is>
-          <t>Table 6. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>STM32F048G6</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>Timers (32-bit) typ</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>Table 6. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>STM32F078VB</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>Table 6. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>STM32F078VB</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>Timers (32-bit) typ</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>Table 6. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>STM32F048C6</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>Table 6. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>STM32F048C6</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>Timers (32-bit) typ</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
         <is>
           <t>Table 6. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>

--- a/product_selector_out/STM32F0x8.xlsx
+++ b/product_selector_out/STM32F0x8.xlsx
@@ -506,7 +506,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BM28"/>
+  <dimension ref="A1:BN28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12.4375" customWidth="1" min="1" max="1"/>
@@ -573,7 +573,8 @@
     <col width="21.765625" customWidth="1" min="62" max="62"/>
     <col width="18" customWidth="1" min="63" max="63"/>
     <col width="18" customWidth="1" min="64" max="64"/>
-    <col width="52" customWidth="1" min="65" max="65"/>
+    <col width="18" customWidth="1" min="65" max="65"/>
+    <col width="52" customWidth="1" min="66" max="66"/>
   </cols>
   <sheetData>
     <row r="1"/>
@@ -901,6 +902,11 @@
         </is>
       </c>
       <c r="BM10" s="2" t="inlineStr">
+        <is>
+          <t>LPUART typ</t>
+        </is>
+      </c>
+      <c r="BN10" s="2" t="inlineStr">
         <is>
           <t>Datasheet URL</t>
         </is>
@@ -996,6 +1002,7 @@
       <c r="BK11" s="2" t="n"/>
       <c r="BL11" s="2" t="n"/>
       <c r="BM11" s="2" t="n"/>
+      <c r="BN11" s="2" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
@@ -1320,6 +1327,11 @@
       </c>
       <c r="BM12" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN12" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f058c8.pdf</t>
         </is>
       </c>
@@ -1647,6 +1659,11 @@
       </c>
       <c r="BM13" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN13" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f038c6.pdf</t>
         </is>
       </c>
@@ -1974,6 +1991,11 @@
       </c>
       <c r="BM14" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN14" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f038c6.pdf</t>
         </is>
       </c>
@@ -2301,6 +2323,11 @@
       </c>
       <c r="BM15" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN15" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f038c6.pdf</t>
         </is>
       </c>
@@ -2628,6 +2655,11 @@
       </c>
       <c r="BM16" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN16" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f098cc.pdf</t>
         </is>
       </c>
@@ -2955,6 +2987,11 @@
       </c>
       <c r="BM17" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN17" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f048c6.pdf</t>
         </is>
       </c>
@@ -3282,6 +3319,11 @@
       </c>
       <c r="BM18" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN18" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f098cc.pdf</t>
         </is>
       </c>
@@ -3609,6 +3651,11 @@
       </c>
       <c r="BM19" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN19" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f038c6.pdf</t>
         </is>
       </c>
@@ -3936,6 +3983,11 @@
       </c>
       <c r="BM20" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN20" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f058c8.pdf</t>
         </is>
       </c>
@@ -4263,6 +4315,11 @@
       </c>
       <c r="BM21" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN21" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f098cc.pdf</t>
         </is>
       </c>
@@ -4590,6 +4647,11 @@
       </c>
       <c r="BM22" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN22" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f078cb.pdf</t>
         </is>
       </c>
@@ -4917,6 +4979,11 @@
       </c>
       <c r="BM23" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN23" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f038c6.pdf</t>
         </is>
       </c>
@@ -5244,6 +5311,11 @@
       </c>
       <c r="BM24" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN24" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f078cb.pdf</t>
         </is>
       </c>
@@ -5571,6 +5643,11 @@
       </c>
       <c r="BM25" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN25" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f058c8.pdf</t>
         </is>
       </c>
@@ -5898,6 +5975,11 @@
       </c>
       <c r="BM26" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN26" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f048c6.pdf</t>
         </is>
       </c>
@@ -6225,6 +6307,11 @@
       </c>
       <c r="BM27" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN27" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f078cb.pdf</t>
         </is>
       </c>
@@ -6552,12 +6639,17 @@
       </c>
       <c r="BM28" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN28" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f048c6.pdf</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="64">
+  <mergeCells count="65">
     <mergeCell ref="P10:P11"/>
     <mergeCell ref="AS10:AS11"/>
     <mergeCell ref="AD10:AD11"/>
@@ -6578,16 +6670,14 @@
     <mergeCell ref="BA10:BA11"/>
     <mergeCell ref="BG10:BG11"/>
     <mergeCell ref="Q10:Q11"/>
-    <mergeCell ref="A1:BM8"/>
     <mergeCell ref="AR10:AR11"/>
+    <mergeCell ref="AT10:AT11"/>
     <mergeCell ref="S10:S11"/>
-    <mergeCell ref="AT10:AT11"/>
+    <mergeCell ref="BI10:BI11"/>
     <mergeCell ref="AV10:AV11"/>
-    <mergeCell ref="A9:BM9"/>
     <mergeCell ref="BB10:BB11"/>
-    <mergeCell ref="BI10:BI11"/>
+    <mergeCell ref="BM10:BM11"/>
     <mergeCell ref="BD10:BD11"/>
-    <mergeCell ref="BM10:BM11"/>
     <mergeCell ref="Y10:Z10"/>
     <mergeCell ref="AC10:AC11"/>
     <mergeCell ref="B10:B11"/>
@@ -6600,6 +6690,7 @@
     <mergeCell ref="AQ10:AQ11"/>
     <mergeCell ref="AW10:AW11"/>
     <mergeCell ref="BH10:BH11"/>
+    <mergeCell ref="BN10:BN11"/>
     <mergeCell ref="AY10:AY11"/>
     <mergeCell ref="BK10:BK11"/>
     <mergeCell ref="A10:A11"/>
@@ -6619,7 +6710,9 @@
     <mergeCell ref="U10:V10"/>
     <mergeCell ref="AG10:AG11"/>
     <mergeCell ref="F10:F11"/>
+    <mergeCell ref="A9:BN9"/>
     <mergeCell ref="H10:H11"/>
+    <mergeCell ref="A1:BN8"/>
     <mergeCell ref="T10:T11"/>
     <mergeCell ref="J10:J11"/>
   </mergeCells>
@@ -6653,7 +6746,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BM28"/>
+  <dimension ref="A1:BN28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -6721,6 +6814,7 @@
     <col width="16" customWidth="1" min="63" max="63"/>
     <col width="16" customWidth="1" min="64" max="64"/>
     <col width="16" customWidth="1" min="65" max="65"/>
+    <col width="16" customWidth="1" min="66" max="66"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -7054,6 +7148,11 @@
         </is>
       </c>
       <c r="BM10" s="2" t="inlineStr">
+        <is>
+          <t>LPUART typ</t>
+        </is>
+      </c>
+      <c r="BN10" s="2" t="inlineStr">
         <is>
           <t>Datasheet URL</t>
         </is>
@@ -7149,6 +7248,7 @@
       <c r="BK11" s="2" t="n"/>
       <c r="BL11" s="2" t="n"/>
       <c r="BM11" s="2" t="n"/>
+      <c r="BN11" s="2" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
@@ -7471,7 +7571,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM12" s="6" t="inlineStr">
+      <c r="BM12" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN12" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -7798,7 +7903,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM13" s="6" t="inlineStr">
+      <c r="BM13" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN13" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -8125,7 +8235,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM14" s="6" t="inlineStr">
+      <c r="BM14" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN14" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -8452,7 +8567,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM15" s="6" t="inlineStr">
+      <c r="BM15" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN15" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -8779,7 +8899,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM16" s="6" t="inlineStr">
+      <c r="BM16" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN16" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -9106,7 +9231,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM17" s="6" t="inlineStr">
+      <c r="BM17" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN17" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -9433,7 +9563,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM18" s="6" t="inlineStr">
+      <c r="BM18" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN18" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -9760,7 +9895,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM19" s="6" t="inlineStr">
+      <c r="BM19" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN19" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -10087,7 +10227,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM20" s="6" t="inlineStr">
+      <c r="BM20" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN20" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -10414,7 +10559,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM21" s="6" t="inlineStr">
+      <c r="BM21" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN21" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -10741,7 +10891,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM22" s="6" t="inlineStr">
+      <c r="BM22" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN22" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -11068,7 +11223,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM23" s="6" t="inlineStr">
+      <c r="BM23" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN23" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -11395,7 +11555,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM24" s="6" t="inlineStr">
+      <c r="BM24" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN24" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -11722,7 +11887,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM25" s="6" t="inlineStr">
+      <c r="BM25" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN25" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -12049,7 +12219,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM26" s="6" t="inlineStr">
+      <c r="BM26" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN26" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -12376,7 +12551,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM27" s="6" t="inlineStr">
+      <c r="BM27" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN27" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -12703,7 +12883,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM28" s="6" t="inlineStr">
+      <c r="BM28" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN28" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -12711,8 +12896,8 @@
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A9:BM9"/>
-    <mergeCell ref="A1:BM8"/>
+    <mergeCell ref="A9:BN9"/>
+    <mergeCell ref="A1:BN8"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
